--- a/import/data_import/PNC00001 UCB-J_consortium/PN000012 UCBJ-NRU/PublicnEUro_PN000012.xlsx
+++ b/import/data_import/PNC00001 UCB-J_consortium/PN000012 UCBJ-NRU/PublicnEUro_PN000012.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PublicnEUro\DataCatalogue\import\data_import\PNC00001 UCB-J_consortium\PN000012 UCBJ-NRU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A171834-F898-48FF-AE8F-3AAF4781612A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79BC75A-FFC4-42C8-B9A6-68A9C2B6622D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="599" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dataset_info" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="98">
   <si>
     <t># bold fields are required</t>
   </si>
@@ -335,6 +335,24 @@
   </si>
   <si>
     <t>Lundbeck Foundation</t>
+  </si>
+  <si>
+    <t>Effects of escitalopram on synaptic density in the healthy human brain: a randomized controlled trial</t>
+  </si>
+  <si>
+    <t>Annette Johansen, Sophia Armand, Pontus Plavén-Sigray, Arafat Nasser, Brice Ozenne, Ida N. Petersen, Sune H. Keller, Jacob Madsen, Vincent Beliveau, Kirsten Møller, Alexandra Vassilieva, Christelle Langley, Claus Svarer, Dea S. Stenbæk, Barbara J. Sahakian and Gitte M. Knudsen</t>
+  </si>
+  <si>
+    <t> 10.1038/s41380-023-02285-8</t>
+  </si>
+  <si>
+    <t>An In Vivo High-Resolution Human Brain Atlas of Synaptic Density</t>
+  </si>
+  <si>
+    <t>Annette Johansen, Vincent Beliveau, Emil Colliander, Nakul Ravi Raval, Vibeke Høyrup Dam, Nic Gillings, Susana Aznar, Claus Svarer, Pontus Plavén-Sigray and Gitte Moos Knudsen</t>
+  </si>
+  <si>
+    <t> 10.1523/JNEUROSCI.1750-23.2024</t>
   </si>
 </sst>
 </file>
@@ -870,7 +888,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1024,9 +1042,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1037,6 +1052,16 @@
     <xf numFmtId="21" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1067,22 +1092,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1308,20 +1323,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="89" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="81"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="85"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="90"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
@@ -1369,7 +1384,7 @@
       <c r="A7" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="88" t="s">
+      <c r="B7" s="93" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="54" t="s">
@@ -1380,8 +1395,8 @@
       <c r="A8" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="89"/>
-      <c r="C8" s="79">
+      <c r="B8" s="94"/>
+      <c r="C8" s="78">
         <v>4.8622685185185185E-2</v>
       </c>
     </row>
@@ -1411,7 +1426,7 @@
       <c r="A11" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="91" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="13"/>
@@ -1437,7 +1452,7 @@
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="87"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="14"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -1461,7 +1476,7 @@
       <c r="A13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="91" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="14"/>
@@ -1487,7 +1502,7 @@
       <c r="A14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="87"/>
+      <c r="B14" s="92"/>
       <c r="C14" s="14"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1617,7 +1632,7 @@
       <c r="B23" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="74" t="s">
+      <c r="C23" s="73" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1705,10 +1720,10 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="91" t="s">
+      <c r="B8" s="79" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1753,7 +1768,7 @@
       <c r="A3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="80" t="s">
         <v>77</v>
       </c>
       <c r="C3" s="1"/>
@@ -2790,89 +2805,89 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="74" t="s">
         <v>59</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="D2" s="75" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="75" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.45">
-      <c r="B4" s="90"/>
-      <c r="D4" s="78" t="s">
+      <c r="B4" s="96"/>
+      <c r="D4" s="77" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B5" s="90"/>
-      <c r="D5" s="76" t="s">
+      <c r="B5" s="96"/>
+      <c r="D5" s="75" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.45">
-      <c r="B6" s="90"/>
-      <c r="D6" s="78" t="s">
+      <c r="B6" s="96"/>
+      <c r="D6" s="77" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B7" s="90"/>
+      <c r="B7" s="96"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B8" s="90"/>
+      <c r="B8" s="96"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="90"/>
+      <c r="B9" s="96"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="90"/>
+      <c r="B10" s="96"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="90"/>
+      <c r="B11" s="96"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="90"/>
+      <c r="B12" s="96"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="90"/>
+      <c r="B13" s="96"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="90"/>
+      <c r="B14" s="96"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="90"/>
+      <c r="B15" s="96"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="90"/>
+      <c r="B16" s="96"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="90"/>
+      <c r="B17" s="96"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="90"/>
+      <c r="B18" s="96"/>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B19" s="90"/>
+      <c r="B19" s="96"/>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B20" s="90"/>
+      <c r="B20" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2923,10 +2938,10 @@
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="81" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="82" t="s">
         <v>84</v>
       </c>
       <c r="C4" s="64" t="s">
@@ -2947,11 +2962,11 @@
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="81" t="s">
         <v>81</v>
       </c>
       <c r="B6" s="63"/>
-      <c r="C6" s="95" t="s">
+      <c r="C6" s="82" t="s">
         <v>83</v>
       </c>
       <c r="D6" s="1"/>
@@ -4004,18 +4019,18 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="83" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="83" t="s">
         <v>89</v>
       </c>
     </row>
@@ -4076,7 +4091,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="84" t="s">
         <v>91</v>
       </c>
       <c r="B4" s="37" t="s">
@@ -5142,16 +5157,32 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="40"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="73"/>
+      <c r="A4" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="65">
+        <v>45208</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="82" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="40"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="73"/>
+      <c r="A5" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="65">
+        <v>45518</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="82" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="29"/>
@@ -6155,6 +6186,10 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" display="https://doi.org/10.1038/s41380-023-02285-8" xr:uid="{2086A916-599C-4546-8DE2-81F6B6A991B9}"/>
+    <hyperlink ref="D5" r:id="rId2" display="https://doi.org/10.1523/JNEUROSCI.1750-23.2024" xr:uid="{3CB5DEA1-4FA5-4117-82D7-5977FB7DE138}"/>
+  </hyperlinks>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
